--- a/data/LCI/Istrate_2024/lci_LIB_raw_materials.xlsx
+++ b/data/LCI/Istrate_2024/lci_LIB_raw_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/regional_minerals_sustainability/data/LCI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/LCI/Istrate_2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3009" documentId="13_ncr:1_{0CD9267C-230F-4C32-BDB0-E201BD3784C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F371B1-D19C-4C02-B1E4-E6989B65B22E}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="3" r:id="rId1"/>
@@ -2928,10 +2928,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2939,12 +2942,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2955,18 +2952,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3295,20 +3295,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C59EE-1777-41E4-AD79-BDA4CD03F3B5}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="160.109375" customWidth="1"/>
+    <col min="4" max="4" width="160.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>115</v>
       </c>
@@ -3334,10 +3334,10 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="s">
         <v>810</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="85" t="s">
         <v>103</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="85"/>
       <c r="B9" s="85"/>
       <c r="C9" s="31" t="s">
@@ -3375,7 +3375,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>106</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="145" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>107</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="85" t="s">
         <v>108</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="85"/>
       <c r="B13" s="85"/>
       <c r="C13" s="50" t="s">
@@ -3427,63 +3427,63 @@
         <v>811</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>813</v>
       </c>
@@ -3513,22 +3513,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="82.109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="18"/>
-    <col min="5" max="5" width="11.6640625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="82.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="18"/>
+    <col min="5" max="5" width="11.6328125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>551</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
         <v>190</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>190</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>190</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>190</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>215</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
         <v>215</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
         <v>106</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="18" t="s">
         <v>106</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
         <v>106</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>107</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
         <v>107</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
         <v>107</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>107</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
         <v>183</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="18" t="s">
         <v>183</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
         <v>183</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
         <v>183</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="18" t="s">
         <v>183</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
         <v>509</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
         <v>509</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="18" t="s">
         <v>509</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="18" t="s">
         <v>509</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
         <v>509</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="18" t="s">
         <v>509</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
         <v>537</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="18" t="s">
         <v>537</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="18" t="s">
         <v>537</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
         <v>538</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="18" t="s">
         <v>538</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F33" s="53"/>
     </row>
   </sheetData>
@@ -4164,32 +4164,32 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="18" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="18"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" style="18" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="18"/>
+    <col min="8" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="25" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>218</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>0.47746145505612281</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>3.6661019176296294</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>3.1353400000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>227</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>8.7482181400380004</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>478</v>
       </c>
@@ -4381,32 +4381,32 @@
         <v>36.330940848363397</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E13" s="53"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="37"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="37"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="37"/>
     </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I33" s="59"/>
     </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I34" s="59"/>
     </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I35" s="59"/>
       <c r="J35" s="55"/>
     </row>
-    <row r="36" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I36" s="59"/>
     </row>
-    <row r="38" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I38" s="55"/>
     </row>
   </sheetData>
@@ -4423,32 +4423,32 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.33203125" customWidth="1"/>
-    <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" customWidth="1"/>
+    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.36328125" customWidth="1"/>
+    <col min="6" max="6" width="40.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="25" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>641</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>555</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>561</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>566</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>571</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>576</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>580</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>585</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>591</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>594</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>598</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>602</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>604</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>609</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>615</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>619</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>624</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>628</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>623</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>634</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>637</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>560</v>
       </c>
@@ -4887,10 +4887,10 @@
         <v>560</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E28" s="18"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D29" s="18" t="s">
         <v>646</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>0.42659550582862726</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C30" s="58"/>
       <c r="D30" s="18" t="s">
         <v>647</v>
@@ -4909,10 +4909,10 @@
         <v>0.57340449417137274</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E33" s="55"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E34" s="55"/>
     </row>
   </sheetData>
@@ -4923,24 +4923,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.44140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.453125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.90625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="9.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.90625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4964,7 +4964,7 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -4983,7 +4983,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
@@ -5023,12 +5023,12 @@
         <v>718</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>234</v>
       </c>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>232</v>
       </c>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>177</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>79</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>31</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>214</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>49</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>174</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>175</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -5350,7 +5350,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -5369,7 +5369,7 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>3</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>7</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>2</v>
       </c>
@@ -5409,12 +5409,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>10</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>232</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>233</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>177</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>79</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>165</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>83</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -5695,7 +5695,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="8"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>1</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>3</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>7</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>2</v>
       </c>
@@ -5756,12 +5756,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>233</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>231</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>177</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>79</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>99</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>165</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>45</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>97</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>85</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>83</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -6187,7 +6187,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
     </row>
-    <row r="55" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>1</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>6</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>3</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>5</v>
       </c>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D58" s="14"/>
     </row>
-    <row r="59" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>7</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>2</v>
       </c>
@@ -6247,12 +6247,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>10</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>231</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>160</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>88</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>90</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>103</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>91</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>94</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>96</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>83</v>
       </c>
@@ -6609,21 +6609,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6877D36A-0BAC-4924-91DD-945153EBE883}">
   <dimension ref="A1:P173"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.44140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.453125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.90625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -6639,7 +6639,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -6679,12 +6679,12 @@
         <v>718</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>246</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>191</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>178</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>133</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>165</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>123</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>214</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>49</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>150</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>212</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>56</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>74</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>128</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -7163,7 +7163,7 @@
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>1</v>
       </c>
@@ -7185,7 +7185,7 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>3</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>11</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>7</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>2</v>
       </c>
@@ -7225,12 +7225,12 @@
         <v>717</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>10</v>
       </c>
@@ -7270,7 +7270,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>245</v>
       </c>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="J32"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>191</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>27</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>178</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>133</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>165</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>123</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>214</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>49</v>
       </c>
@@ -7541,7 +7541,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>150</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>212</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>56</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>74</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>128</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -7716,7 +7716,7 @@
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
     </row>
-    <row r="47" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>1</v>
       </c>
@@ -7732,7 +7732,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>6</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>3</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>11</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>7</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>2</v>
       </c>
@@ -7772,12 +7772,12 @@
         <v>715</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>10</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>191</v>
       </c>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="J55"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>210</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>31</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>216</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>178</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>71</v>
       </c>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>196</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>199</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>201</v>
       </c>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="M63" s="6"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>129</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>203</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>127</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>142</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>16</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>174</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>176</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>175</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>204</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="27" t="s">
         <v>91</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="27" t="s">
         <v>105</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="27" t="s">
         <v>205</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="76" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="27" t="s">
         <v>96</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="27" t="s">
         <v>171</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="27" t="s">
         <v>181</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="27" t="s">
         <v>188</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>74</v>
       </c>
@@ -8629,7 +8629,7 @@
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>174</v>
       </c>
@@ -8661,7 +8661,7 @@
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>176</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>175</v>
       </c>
@@ -8725,241 +8725,241 @@
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D95" s="15"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E109" s="14"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D113" s="14"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D114" s="14"/>
       <c r="E114" s="14"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E117" s="14"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="14"/>
       <c r="D118" s="14"/>
       <c r="F118" s="14"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="14"/>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="14"/>
       <c r="F120" s="14"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="14"/>
       <c r="F121" s="14"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="14"/>
       <c r="F122" s="14"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="14"/>
       <c r="F123" s="14"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="14"/>
       <c r="F124" s="14"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="14"/>
       <c r="F125" s="14"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="14"/>
       <c r="F126" s="14"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="14"/>
       <c r="F127" s="14"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="14"/>
       <c r="F128" s="14"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="14"/>
       <c r="F129" s="14"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="14"/>
       <c r="F130" s="14"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="14"/>
       <c r="F131" s="14"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="14"/>
       <c r="F132" s="14"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="14"/>
       <c r="F133" s="14"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="14"/>
       <c r="F134" s="14"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="14"/>
       <c r="F135" s="14"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="14"/>
       <c r="F136" s="14"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="14"/>
       <c r="F137" s="14"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="14"/>
       <c r="F138" s="14"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F139" s="14"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="14"/>
       <c r="F140" s="14"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="14"/>
       <c r="F141" s="14"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="14"/>
       <c r="F142" s="14"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="14"/>
       <c r="F143" s="14"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="14"/>
       <c r="F144" s="14"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F145" s="14"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="14"/>
       <c r="F146" s="14"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="14"/>
       <c r="F147" s="14"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="14"/>
       <c r="F148" s="14"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="14"/>
       <c r="F149" s="14"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="14"/>
       <c r="F150" s="14"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="14"/>
       <c r="F151" s="14"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="14"/>
       <c r="F152" s="14"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="14"/>
       <c r="F153" s="14"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="14"/>
       <c r="F154" s="14"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="14"/>
       <c r="F155" s="14"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="14"/>
       <c r="F156" s="14"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="14"/>
       <c r="F157" s="14"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="14"/>
       <c r="F158" s="14"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F159" s="14"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="14"/>
       <c r="F160" s="14"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="14"/>
       <c r="F161" s="14"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="14"/>
       <c r="F162" s="14"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="14"/>
       <c r="F163" s="14"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="14"/>
       <c r="F164" s="14"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="14"/>
       <c r="F165" s="14"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="14"/>
       <c r="F166" s="14"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="14"/>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="14"/>
       <c r="F168" s="14"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="14"/>
       <c r="F169" s="14"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="14"/>
       <c r="F170" s="14"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="14"/>
       <c r="F171" s="14"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="14"/>
       <c r="F172" s="14"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="14"/>
       <c r="F173" s="14"/>
     </row>
@@ -8972,21 +8972,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7526F10-A44B-4159-997F-0A6BAB3CF087}">
   <dimension ref="A1:XFA86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.90625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -15143,7 +15143,7 @@
       <c r="XEZ1" s="17"/>
       <c r="XFA1" s="17"/>
     </row>
-    <row r="2" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -15167,7 +15167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -15183,12 +15183,12 @@
         <v>473</v>
       </c>
     </row>
-    <row r="7" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>472</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="10" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>471</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="11" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="12" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>256</v>
       </c>
@@ -15371,7 +15371,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="14" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>477</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="15" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>138</v>
       </c>
@@ -15431,7 +15431,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="16" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>45</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="17" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>85</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="18" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>51</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="19" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>135</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="20" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>140</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="21" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>123</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="22" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>133</v>
       </c>
@@ -15641,7 +15641,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="23" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>142</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="24" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>144</v>
       </c>
@@ -15701,7 +15701,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="25" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
@@ -15731,7 +15731,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="26" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>146</v>
       </c>
@@ -15761,7 +15761,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="27" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>56</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="28" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>150</v>
       </c>
@@ -15821,7 +15821,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="29" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>152</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="30" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>54</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="31" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -15887,7 +15887,7 @@
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>1</v>
       </c>
@@ -22044,7 +22044,7 @@
       <c r="XEZ32" s="17"/>
       <c r="XFA32" s="17"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>6</v>
       </c>
@@ -22063,7 +22063,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>3</v>
       </c>
@@ -22082,7 +22082,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>5</v>
       </c>
@@ -22101,7 +22101,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>7</v>
       </c>
@@ -22120,7 +22120,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>2</v>
       </c>
@@ -22139,7 +22139,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>9</v>
       </c>
@@ -22153,7 +22153,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>10</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>471</v>
       </c>
@@ -22213,7 +22213,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>469</v>
       </c>
@@ -22244,7 +22244,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>177</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>117</v>
       </c>
@@ -22304,7 +22304,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>119</v>
       </c>
@@ -22334,7 +22334,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>121</v>
       </c>
@@ -22364,7 +22364,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>123</v>
       </c>
@@ -22394,7 +22394,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>125</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>127</v>
       </c>
@@ -22451,7 +22451,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="49" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>16</v>
       </c>
@@ -22478,7 +22478,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>129</v>
       </c>
@@ -22502,7 +22502,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="51" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>130</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="52" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>83</v>
       </c>
@@ -22554,7 +22554,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="53" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>128</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="54" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -22593,7 +22593,7 @@
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
     </row>
-    <row r="55" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>1</v>
       </c>
@@ -28750,7 +28750,7 @@
       <c r="XEZ55" s="17"/>
       <c r="XFA55" s="17"/>
     </row>
-    <row r="56" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>6</v>
       </c>
@@ -28769,7 +28769,7 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>3</v>
       </c>
@@ -28788,7 +28788,7 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>5</v>
       </c>
@@ -28807,7 +28807,7 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>7</v>
       </c>
@@ -28826,7 +28826,7 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
     </row>
-    <row r="60" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>2</v>
       </c>
@@ -28845,7 +28845,7 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
     </row>
-    <row r="61" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>9</v>
       </c>
@@ -28862,7 +28862,7 @@
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
     </row>
-    <row r="62" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>10</v>
       </c>
@@ -28900,7 +28900,7 @@
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
     </row>
-    <row r="63" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>469</v>
       </c>
@@ -28928,7 +28928,7 @@
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
     </row>
-    <row r="64" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1021 1027:2045 2051:3069 3075:4093 4099:5117 5123:6141 6147:7165 7171:8189 8195:9213 9219:10237 10243:11261 11267:12285 12291:13309 13315:14333 14339:15357 15363:16381" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>31</v>
       </c>
@@ -28962,7 +28962,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>106</v>
       </c>
@@ -28994,7 +28994,7 @@
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>173</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>83</v>
       </c>
@@ -29049,7 +29049,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>175</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>174</v>
       </c>
@@ -29103,28 +29103,28 @@
         <v>754</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F76" s="49"/>
       <c r="G76" s="49"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G77" s="48"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B78" s="14"/>
       <c r="G78" s="48"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B79" s="14"/>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G81" s="48"/>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B83" s="14"/>
       <c r="G83" s="49"/>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B86" s="14"/>
     </row>
   </sheetData>
@@ -29136,21 +29136,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A386841A-7D2F-44FE-BC7D-453E0B437B7D}">
   <dimension ref="A1:AS303"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" customWidth="1"/>
-    <col min="2" max="2" width="49.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="57.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="29"/>
+    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.08984375" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -29167,7 +29167,7 @@
       <c r="J1"/>
       <c r="K1" s="29"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -29175,7 +29175,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -29183,7 +29183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -29191,7 +29191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -29199,7 +29199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -29207,12 +29207,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -29247,7 +29247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>418</v>
       </c>
@@ -29275,7 +29275,7 @@
       <c r="J9"/>
       <c r="K9" s="29"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>388</v>
       </c>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="N10" s="38"/>
     </row>
-    <row r="11" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
         <v>27</v>
       </c>
@@ -29336,7 +29336,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -29369,7 +29369,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>273</v>
       </c>
@@ -29402,7 +29402,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>274</v>
       </c>
@@ -29435,7 +29435,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>274</v>
       </c>
@@ -29468,7 +29468,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>271</v>
       </c>
@@ -29501,7 +29501,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>298</v>
       </c>
@@ -29531,7 +29531,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -29564,7 +29564,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" s="27" t="s">
         <v>433</v>
       </c>
@@ -29598,7 +29598,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>277</v>
       </c>
@@ -29645,7 +29645,7 @@
       <c r="W20"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>280</v>
       </c>
@@ -29676,7 +29676,7 @@
       </c>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>285</v>
       </c>
@@ -29706,7 +29706,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>287</v>
       </c>
@@ -29739,7 +29739,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>287</v>
       </c>
@@ -29772,7 +29772,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>291</v>
       </c>
@@ -29802,7 +29802,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>293</v>
       </c>
@@ -29832,7 +29832,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -29862,7 +29862,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>300</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>302</v>
       </c>
@@ -29922,7 +29922,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>379</v>
       </c>
@@ -29952,7 +29952,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>304</v>
       </c>
@@ -29982,7 +29982,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>309</v>
       </c>
@@ -30016,7 +30016,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>312</v>
       </c>
@@ -30046,7 +30046,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>317</v>
       </c>
@@ -30079,7 +30079,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>165</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>320</v>
       </c>
@@ -30139,7 +30139,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
         <v>322</v>
       </c>
@@ -30169,7 +30169,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
         <v>322</v>
       </c>
@@ -30202,7 +30202,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>123</v>
       </c>
@@ -30232,7 +30232,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>324</v>
       </c>
@@ -30265,7 +30265,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>327</v>
       </c>
@@ -30295,7 +30295,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>169</v>
       </c>
@@ -30325,7 +30325,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>133</v>
       </c>
@@ -30355,7 +30355,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>167</v>
       </c>
@@ -30388,7 +30388,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>306</v>
       </c>
@@ -30435,7 +30435,7 @@
       <c r="W45"/>
       <c r="X45"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>314</v>
       </c>
@@ -30468,7 +30468,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>282</v>
       </c>
@@ -30501,7 +30501,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -30534,7 +30534,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
         <v>37</v>
       </c>
@@ -30561,7 +30561,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
         <v>76</v>
       </c>
@@ -30588,7 +30588,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -30615,7 +30615,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>182</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>74</v>
       </c>
@@ -30669,7 +30669,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -30696,7 +30696,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>174</v>
       </c>
@@ -30723,7 +30723,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>176</v>
       </c>
@@ -30750,7 +30750,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>175</v>
       </c>
@@ -30777,7 +30777,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -30804,7 +30804,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>330</v>
       </c>
@@ -30831,7 +30831,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>188</v>
       </c>
@@ -30858,7 +30858,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>391</v>
       </c>
@@ -30885,7 +30885,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>392</v>
       </c>
@@ -30912,7 +30912,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>393</v>
       </c>
@@ -30939,7 +30939,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>419</v>
       </c>
@@ -30966,7 +30966,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>394</v>
       </c>
@@ -30993,7 +30993,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>395</v>
       </c>
@@ -31020,7 +31020,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>396</v>
       </c>
@@ -31047,7 +31047,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>398</v>
       </c>
@@ -31074,7 +31074,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>399</v>
       </c>
@@ -31101,7 +31101,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>400</v>
       </c>
@@ -31128,7 +31128,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>401</v>
       </c>
@@ -31155,7 +31155,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>402</v>
       </c>
@@ -31182,7 +31182,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>54</v>
       </c>
@@ -31209,7 +31209,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>54</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -31263,7 +31263,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>332</v>
       </c>
@@ -31290,7 +31290,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>172</v>
       </c>
@@ -31317,7 +31317,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -31344,7 +31344,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -31371,7 +31371,7 @@
       <c r="X79" s="36"/>
       <c r="Y79" s="36"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>1</v>
       </c>
@@ -31379,7 +31379,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -31387,7 +31387,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -31395,7 +31395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -31403,7 +31403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>7</v>
       </c>
@@ -31411,7 +31411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>2</v>
       </c>
@@ -31419,12 +31419,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>10</v>
       </c>
@@ -31459,7 +31459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>388</v>
       </c>
@@ -31483,7 +31483,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>376</v>
       </c>
@@ -31513,7 +31513,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="90" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="29" t="s">
         <v>27</v>
       </c>
@@ -31544,7 +31544,7 @@
       </c>
       <c r="M90"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>168</v>
       </c>
@@ -31577,7 +31577,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="92" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>273</v>
       </c>
@@ -31613,7 +31613,7 @@
       <c r="L92"/>
       <c r="M92"/>
     </row>
-    <row r="93" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>274</v>
       </c>
@@ -31649,7 +31649,7 @@
       <c r="L93"/>
       <c r="M93"/>
     </row>
-    <row r="94" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>274</v>
       </c>
@@ -31685,7 +31685,7 @@
       <c r="L94"/>
       <c r="M94"/>
     </row>
-    <row r="95" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="29" t="s">
         <v>463</v>
       </c>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="M95"/>
     </row>
-    <row r="96" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="29" t="s">
         <v>433</v>
       </c>
@@ -31747,7 +31747,7 @@
       </c>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="29" t="s">
         <v>465</v>
       </c>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="M97"/>
     </row>
-    <row r="98" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -31809,7 +31809,7 @@
       </c>
       <c r="M98"/>
     </row>
-    <row r="99" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A99" s="29" t="s">
         <v>390</v>
       </c>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="M99" s="45"/>
     </row>
-    <row r="100" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>456</v>
       </c>
@@ -31876,7 +31876,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>125</v>
       </c>
@@ -31909,7 +31909,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>334</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>335</v>
       </c>
@@ -31972,7 +31972,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>280</v>
       </c>
@@ -32002,7 +32002,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>336</v>
       </c>
@@ -32035,7 +32035,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>287</v>
       </c>
@@ -32068,7 +32068,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>340</v>
       </c>
@@ -32098,7 +32098,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>342</v>
       </c>
@@ -32131,7 +32131,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>45</v>
       </c>
@@ -32161,7 +32161,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>300</v>
       </c>
@@ -32191,7 +32191,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>302</v>
       </c>
@@ -32221,7 +32221,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>345</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>348</v>
       </c>
@@ -32287,7 +32287,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>351</v>
       </c>
@@ -32317,7 +32317,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>353</v>
       </c>
@@ -32350,7 +32350,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>135</v>
       </c>
@@ -32380,7 +32380,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>306</v>
       </c>
@@ -32413,7 +32413,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>47</v>
       </c>
@@ -32443,7 +32443,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>32</v>
       </c>
@@ -32473,7 +32473,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>312</v>
       </c>
@@ -32503,7 +32503,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>317</v>
       </c>
@@ -32536,7 +32536,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>165</v>
       </c>
@@ -32566,7 +32566,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -32596,7 +32596,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>167</v>
       </c>
@@ -32629,7 +32629,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>358</v>
       </c>
@@ -32662,7 +32662,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>148</v>
       </c>
@@ -32695,7 +32695,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>355</v>
       </c>
@@ -32728,7 +32728,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>360</v>
       </c>
@@ -32758,7 +32758,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>417</v>
       </c>
@@ -32791,7 +32791,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="130" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="29" t="s">
         <v>37</v>
       </c>
@@ -32821,7 +32821,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>76</v>
       </c>
@@ -32849,7 +32849,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>77</v>
       </c>
@@ -32876,7 +32876,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>182</v>
       </c>
@@ -32903,7 +32903,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>74</v>
       </c>
@@ -32930,7 +32930,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>74</v>
       </c>
@@ -32960,7 +32960,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>176</v>
       </c>
@@ -32987,7 +32987,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>175</v>
       </c>
@@ -33014,7 +33014,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>128</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>363</v>
       </c>
@@ -33071,7 +33071,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>330</v>
       </c>
@@ -33098,7 +33098,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>330</v>
       </c>
@@ -33125,7 +33125,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>391</v>
       </c>
@@ -33153,7 +33153,7 @@
       </c>
       <c r="M142" s="40"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>392</v>
       </c>
@@ -33181,7 +33181,7 @@
       </c>
       <c r="M143" s="40"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>393</v>
       </c>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="M144" s="40"/>
     </row>
-    <row r="145" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>394</v>
       </c>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="M145" s="40"/>
     </row>
-    <row r="146" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>395</v>
       </c>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="M146" s="40"/>
     </row>
-    <row r="147" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>396</v>
       </c>
@@ -33293,7 +33293,7 @@
       </c>
       <c r="M147" s="40"/>
     </row>
-    <row r="148" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>362</v>
       </c>
@@ -33320,7 +33320,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="149" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>398</v>
       </c>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="M149" s="40"/>
     </row>
-    <row r="150" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>399</v>
       </c>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="M150" s="40"/>
     </row>
-    <row r="151" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>400</v>
       </c>
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M151" s="40"/>
     </row>
-    <row r="152" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>401</v>
       </c>
@@ -33431,7 +33431,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="153" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>402</v>
       </c>
@@ -33458,7 +33458,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="154" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>54</v>
       </c>
@@ -33485,7 +33485,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="155" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>54</v>
       </c>
@@ -33512,7 +33512,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="156" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>332</v>
       </c>
@@ -33539,7 +33539,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="157" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>365</v>
       </c>
@@ -33566,7 +33566,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -33593,7 +33593,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="159" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>83</v>
       </c>
@@ -33620,7 +33620,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="35"/>
       <c r="B160" s="35"/>
       <c r="C160" s="35"/>
@@ -33667,7 +33667,7 @@
       <c r="AR160" s="36"/>
       <c r="AS160" s="36"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>1</v>
       </c>
@@ -33675,7 +33675,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>6</v>
       </c>
@@ -33683,7 +33683,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>3</v>
       </c>
@@ -33691,7 +33691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -33699,7 +33699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>7</v>
       </c>
@@ -33707,7 +33707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>2</v>
       </c>
@@ -33715,12 +33715,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>10</v>
       </c>
@@ -33755,7 +33755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>376</v>
       </c>
@@ -33779,7 +33779,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>377</v>
       </c>
@@ -33809,7 +33809,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="171" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A171" s="29" t="s">
         <v>27</v>
       </c>
@@ -33840,7 +33840,7 @@
       </c>
       <c r="M171"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>296</v>
       </c>
@@ -33873,7 +33873,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>271</v>
       </c>
@@ -33906,7 +33906,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>273</v>
       </c>
@@ -33939,7 +33939,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>274</v>
       </c>
@@ -33972,7 +33972,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>64</v>
       </c>
@@ -34005,7 +34005,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="27" t="s">
         <v>433</v>
       </c>
@@ -34039,7 +34039,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>277</v>
       </c>
@@ -34072,7 +34072,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>351</v>
       </c>
@@ -34105,7 +34105,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>304</v>
       </c>
@@ -34138,7 +34138,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>47</v>
       </c>
@@ -34168,7 +34168,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>165</v>
       </c>
@@ -34201,7 +34201,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>322</v>
       </c>
@@ -34234,7 +34234,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>324</v>
       </c>
@@ -34267,7 +34267,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>133</v>
       </c>
@@ -34297,7 +34297,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>306</v>
       </c>
@@ -34330,7 +34330,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -34363,7 +34363,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>314</v>
       </c>
@@ -34396,7 +34396,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>282</v>
       </c>
@@ -34429,7 +34429,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>148</v>
       </c>
@@ -34462,7 +34462,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>366</v>
       </c>
@@ -34495,7 +34495,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="192" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A192" s="29" t="s">
         <v>37</v>
       </c>
@@ -34525,7 +34525,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="193" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A193" s="29" t="s">
         <v>76</v>
       </c>
@@ -34555,7 +34555,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="194" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A194" s="29" t="s">
         <v>77</v>
       </c>
@@ -34585,7 +34585,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="195" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:37" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="29" t="s">
         <v>182</v>
       </c>
@@ -34612,7 +34612,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="196" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>74</v>
       </c>
@@ -34639,7 +34639,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="197" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>174</v>
       </c>
@@ -34669,7 +34669,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>176</v>
       </c>
@@ -34696,7 +34696,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="199" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>175</v>
       </c>
@@ -34723,7 +34723,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="200" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>128</v>
       </c>
@@ -34750,7 +34750,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="201" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>54</v>
       </c>
@@ -34777,7 +34777,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="202" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A202" s="35"/>
       <c r="B202" s="35"/>
       <c r="C202" s="35"/>
@@ -34816,7 +34816,7 @@
       <c r="AJ202" s="36"/>
       <c r="AK202" s="36"/>
     </row>
-    <row r="203" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>1</v>
       </c>
@@ -34824,7 +34824,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="204" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>6</v>
       </c>
@@ -34832,7 +34832,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="205" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>3</v>
       </c>
@@ -34840,7 +34840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>5</v>
       </c>
@@ -34848,7 +34848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>7</v>
       </c>
@@ -34856,7 +34856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>2</v>
       </c>
@@ -34864,12 +34864,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>10</v>
       </c>
@@ -34904,7 +34904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>377</v>
       </c>
@@ -34929,7 +34929,7 @@
       </c>
       <c r="I211" s="6"/>
     </row>
-    <row r="212" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="29" t="s">
         <v>27</v>
       </c>
@@ -34963,7 +34963,7 @@
       </c>
       <c r="M212"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>274</v>
       </c>
@@ -34996,7 +34996,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>287</v>
       </c>
@@ -35029,7 +35029,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>64</v>
       </c>
@@ -35062,7 +35062,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="27" t="s">
         <v>433</v>
       </c>
@@ -35096,7 +35096,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>71</v>
       </c>
@@ -35129,7 +35129,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>306</v>
       </c>
@@ -35162,7 +35162,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>314</v>
       </c>
@@ -35195,7 +35195,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>282</v>
       </c>
@@ -35228,7 +35228,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -35261,7 +35261,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>368</v>
       </c>
@@ -35294,7 +35294,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="223" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" s="29" t="s">
         <v>37</v>
       </c>
@@ -35324,7 +35324,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="224" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A224" s="29" t="s">
         <v>76</v>
       </c>
@@ -35354,7 +35354,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>77</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>182</v>
       </c>
@@ -35414,7 +35414,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>74</v>
       </c>
@@ -35444,7 +35444,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>74</v>
       </c>
@@ -35474,7 +35474,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>176</v>
       </c>
@@ -35504,7 +35504,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>175</v>
       </c>
@@ -35534,7 +35534,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>128</v>
       </c>
@@ -35564,7 +35564,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>107</v>
       </c>
@@ -35591,7 +35591,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>107</v>
       </c>
@@ -35618,7 +35618,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>106</v>
       </c>
@@ -35645,7 +35645,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>173</v>
       </c>
@@ -35672,7 +35672,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>204</v>
       </c>
@@ -35702,7 +35702,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>381</v>
       </c>
@@ -35729,7 +35729,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>382</v>
       </c>
@@ -35756,7 +35756,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>386</v>
       </c>
@@ -35783,7 +35783,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>383</v>
       </c>
@@ -35810,7 +35810,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="241" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>384</v>
       </c>
@@ -35837,7 +35837,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="242" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>54</v>
       </c>
@@ -35867,7 +35867,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="243" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A243" s="35"/>
       <c r="B243" s="35"/>
       <c r="C243" s="35"/>
@@ -35906,7 +35906,7 @@
       <c r="AJ243" s="36"/>
       <c r="AK243" s="36"/>
     </row>
-    <row r="244" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A244" s="41" t="s">
         <v>1</v>
       </c>
@@ -35914,7 +35914,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="245" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A245" s="41" t="s">
         <v>6</v>
       </c>
@@ -35922,7 +35922,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="246" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>3</v>
       </c>
@@ -35930,7 +35930,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>5</v>
       </c>
@@ -35938,7 +35938,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="248" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>7</v>
       </c>
@@ -35946,12 +35946,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -35986,7 +35986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>417</v>
       </c>
@@ -36010,7 +36010,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="252" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>277</v>
       </c>
@@ -36034,7 +36034,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="253" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>277</v>
       </c>
@@ -36058,7 +36058,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="254" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>403</v>
       </c>
@@ -36082,7 +36082,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="255" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>45</v>
       </c>
@@ -36106,7 +36106,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="256" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>300</v>
       </c>
@@ -36130,7 +36130,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>353</v>
       </c>
@@ -36154,7 +36154,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>304</v>
       </c>
@@ -36178,7 +36178,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>123</v>
       </c>
@@ -36202,7 +36202,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>133</v>
       </c>
@@ -36226,7 +36226,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>391</v>
       </c>
@@ -36247,7 +36247,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>392</v>
       </c>
@@ -36268,7 +36268,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>392</v>
       </c>
@@ -36289,7 +36289,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -36310,7 +36310,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>406</v>
       </c>
@@ -36331,7 +36331,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>407</v>
       </c>
@@ -36352,7 +36352,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>407</v>
       </c>
@@ -36373,7 +36373,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>393</v>
       </c>
@@ -36394,7 +36394,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>393</v>
       </c>
@@ -36415,7 +36415,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>408</v>
       </c>
@@ -36436,7 +36436,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>394</v>
       </c>
@@ -36457,7 +36457,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>394</v>
       </c>
@@ -36478,7 +36478,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>394</v>
       </c>
@@ -36499,7 +36499,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>395</v>
       </c>
@@ -36520,7 +36520,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>395</v>
       </c>
@@ -36541,7 +36541,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>396</v>
       </c>
@@ -36562,7 +36562,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>396</v>
       </c>
@@ -36583,7 +36583,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>409</v>
       </c>
@@ -36604,7 +36604,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>420</v>
       </c>
@@ -36625,7 +36625,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>398</v>
       </c>
@@ -36646,7 +36646,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>398</v>
       </c>
@@ -36667,7 +36667,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>410</v>
       </c>
@@ -36688,7 +36688,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>397</v>
       </c>
@@ -36709,7 +36709,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>397</v>
       </c>
@@ -36730,7 +36730,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>400</v>
       </c>
@@ -36751,7 +36751,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>400</v>
       </c>
@@ -36772,7 +36772,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>401</v>
       </c>
@@ -36793,7 +36793,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>411</v>
       </c>
@@ -36814,7 +36814,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>411</v>
       </c>
@@ -36835,7 +36835,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>412</v>
       </c>
@@ -36856,7 +36856,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>421</v>
       </c>
@@ -36877,7 +36877,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>423</v>
       </c>
@@ -36898,7 +36898,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>413</v>
       </c>
@@ -36919,7 +36919,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>413</v>
       </c>
@@ -36940,7 +36940,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>330</v>
       </c>
@@ -36961,7 +36961,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>414</v>
       </c>
@@ -36982,7 +36982,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>415</v>
       </c>
@@ -37003,7 +37003,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>415</v>
       </c>
@@ -37024,7 +37024,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>422</v>
       </c>
@@ -37045,7 +37045,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>54</v>
       </c>
@@ -37066,7 +37066,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>54</v>
       </c>
@@ -37087,7 +37087,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>54</v>
       </c>
@@ -37108,7 +37108,7 @@
         <v>ecoinvent-3.10-biosphere</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>402</v>
       </c>
@@ -37138,24 +37138,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3D24D4-2E6F-41D5-89DB-3F789653CF27}">
   <dimension ref="A1:S87"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.44140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="6"/>
-    <col min="6" max="6" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.88671875" style="6"/>
-    <col min="19" max="19" width="21.88671875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="46.453125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="33.36328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="6"/>
+    <col min="6" max="6" width="13.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.90625" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.90625" style="6"/>
+    <col min="19" max="19" width="21.90625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -37163,7 +37163,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -37171,7 +37171,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -37179,7 +37179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -37187,7 +37187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -37195,7 +37195,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -37203,12 +37203,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -37250,7 +37250,7 @@
       </c>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>155</v>
       </c>
@@ -37278,7 +37278,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>157</v>
       </c>
@@ -37310,7 +37310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -37353,7 +37353,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
@@ -37440,7 +37440,7 @@
       </c>
       <c r="N13"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>35</v>
       </c>
@@ -37483,7 +37483,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
@@ -37515,7 +37515,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
@@ -37544,7 +37544,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>41</v>
       </c>
@@ -37573,7 +37573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -37584,7 +37584,7 @@
       <c r="N18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>1</v>
       </c>
@@ -37592,7 +37592,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -37600,7 +37600,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
@@ -37608,7 +37608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -37616,7 +37616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>7</v>
       </c>
@@ -37624,7 +37624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
@@ -37632,12 +37632,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>157</v>
       </c>
@@ -37707,7 +37707,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>53</v>
       </c>
@@ -37750,7 +37750,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
@@ -37793,7 +37793,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
@@ -37836,7 +37836,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>79</v>
       </c>
@@ -37883,7 +37883,7 @@
       <c r="Q31" s="6"/>
       <c r="S31"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>252</v>
       </c>
@@ -37926,7 +37926,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>45</v>
       </c>
@@ -37969,7 +37969,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>47</v>
       </c>
@@ -38012,7 +38012,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>49</v>
       </c>
@@ -38055,7 +38055,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>51</v>
       </c>
@@ -38098,7 +38098,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>56</v>
       </c>
@@ -38127,7 +38127,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>54</v>
       </c>
@@ -38156,7 +38156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -38167,7 +38167,7 @@
       <c r="N39" s="8"/>
       <c r="S39" s="8"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>1</v>
       </c>
@@ -38175,7 +38175,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>6</v>
       </c>
@@ -38183,7 +38183,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>3</v>
       </c>
@@ -38191,7 +38191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>5</v>
       </c>
@@ -38199,7 +38199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>7</v>
       </c>
@@ -38207,7 +38207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>21</v>
       </c>
@@ -38215,12 +38215,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>10</v>
       </c>
@@ -38262,7 +38262,7 @@
       </c>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>53</v>
       </c>
@@ -38291,7 +38291,7 @@
       <c r="L48" s="6"/>
       <c r="S48" s="60"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>58</v>
       </c>
@@ -38334,7 +38334,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>27</v>
       </c>
@@ -38377,7 +38377,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>31</v>
       </c>
@@ -38420,7 +38420,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -38431,7 +38431,7 @@
       <c r="N52" s="8"/>
       <c r="S52" s="8"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>1</v>
       </c>
@@ -38439,7 +38439,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>6</v>
       </c>
@@ -38447,7 +38447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>3</v>
       </c>
@@ -38455,7 +38455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>5</v>
       </c>
@@ -38463,7 +38463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>7</v>
       </c>
@@ -38471,7 +38471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>2</v>
       </c>
@@ -38479,12 +38479,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>10</v>
       </c>
@@ -38526,7 +38526,7 @@
       </c>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>58</v>
       </c>
@@ -38554,7 +38554,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>61</v>
       </c>
@@ -38586,7 +38586,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>27</v>
       </c>
@@ -38629,7 +38629,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>178</v>
       </c>
@@ -38672,7 +38672,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>31</v>
       </c>
@@ -38715,7 +38715,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>456</v>
       </c>
@@ -38758,7 +38758,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>49</v>
       </c>
@@ -38801,7 +38801,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>56</v>
       </c>
@@ -38833,7 +38833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>67</v>
       </c>
@@ -38862,7 +38862,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>23</v>
       </c>
@@ -38894,7 +38894,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>54</v>
       </c>
@@ -38923,7 +38923,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -38934,7 +38934,7 @@
       <c r="N72" s="8"/>
       <c r="S72" s="8"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>1</v>
       </c>
@@ -38942,7 +38942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>6</v>
       </c>
@@ -38950,7 +38950,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>3</v>
       </c>
@@ -38958,7 +38958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>5</v>
       </c>
@@ -38966,7 +38966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>7</v>
       </c>
@@ -38974,7 +38974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>2</v>
       </c>
@@ -38982,12 +38982,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>10</v>
       </c>
@@ -39029,7 +39029,7 @@
       </c>
       <c r="N80" s="5"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>61</v>
       </c>
@@ -39057,7 +39057,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>27</v>
       </c>
@@ -39100,7 +39100,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>31</v>
       </c>
@@ -39143,7 +39143,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>71</v>
       </c>
@@ -39186,7 +39186,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>54</v>
       </c>
@@ -39215,7 +39215,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>74</v>
       </c>
@@ -39244,7 +39244,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>176</v>
       </c>
@@ -39282,22 +39282,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024CCAE1-AADE-4D85-A6C2-DF07BF45D505}">
   <dimension ref="A1:Q97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="48.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.90625" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -39312,7 +39312,7 @@
       <c r="L1" s="6"/>
       <c r="Q1" s="6"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -39327,7 +39327,7 @@
       <c r="L2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -39342,7 +39342,7 @@
       <c r="L3" s="6"/>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -39357,7 +39357,7 @@
       <c r="L4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -39372,7 +39372,7 @@
       <c r="L5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -39387,7 +39387,7 @@
       <c r="L6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -39400,7 +39400,7 @@
       <c r="L7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -39436,7 +39436,7 @@
       </c>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>490</v>
       </c>
@@ -39466,7 +39466,7 @@
       <c r="L9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="27" t="s">
         <v>487</v>
       </c>
@@ -39502,7 +39502,7 @@
       <c r="L10" s="27"/>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>491</v>
       </c>
@@ -39535,7 +39535,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>27</v>
       </c>
@@ -39572,7 +39572,7 @@
       <c r="L12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>79</v>
       </c>
@@ -39611,7 +39611,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>498</v>
       </c>
@@ -39648,7 +39648,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>501</v>
       </c>
@@ -39686,7 +39686,7 @@
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>503</v>
       </c>
@@ -39724,7 +39724,7 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
@@ -39757,7 +39757,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -39768,7 +39768,7 @@
       <c r="L18" s="8"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>1</v>
       </c>
@@ -39783,7 +39783,7 @@
       <c r="L19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -39798,7 +39798,7 @@
       <c r="L20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
@@ -39813,7 +39813,7 @@
       <c r="L21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -39828,7 +39828,7 @@
       <c r="L22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>7</v>
       </c>
@@ -39843,7 +39843,7 @@
       <c r="L23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
@@ -39858,7 +39858,7 @@
       <c r="L24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>9</v>
       </c>
@@ -39871,7 +39871,7 @@
       <c r="L25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -39907,7 +39907,7 @@
       </c>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>487</v>
       </c>
@@ -39937,7 +39937,7 @@
       <c r="L27" s="6"/>
       <c r="Q27" s="6"/>
     </row>
-    <row r="28" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="27" t="s">
         <v>486</v>
       </c>
@@ -39974,7 +39974,7 @@
       <c r="L28" s="27"/>
       <c r="Q28" s="27"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
@@ -40011,7 +40011,7 @@
       <c r="L29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>79</v>
       </c>
@@ -40050,7 +40050,7 @@
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -40061,7 +40061,7 @@
       <c r="L31" s="8"/>
       <c r="Q31" s="8"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>1</v>
       </c>
@@ -40076,7 +40076,7 @@
       <c r="L32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>6</v>
       </c>
@@ -40091,7 +40091,7 @@
       <c r="L33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>3</v>
       </c>
@@ -40106,7 +40106,7 @@
       <c r="L34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>5</v>
       </c>
@@ -40121,7 +40121,7 @@
       <c r="L35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -40136,7 +40136,7 @@
       <c r="L36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>2</v>
       </c>
@@ -40151,7 +40151,7 @@
       <c r="L37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
@@ -40164,7 +40164,7 @@
       <c r="L38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>10</v>
       </c>
@@ -40200,7 +40200,7 @@
       </c>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>486</v>
       </c>
@@ -40230,7 +40230,7 @@
       <c r="L40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
         <v>483</v>
       </c>
@@ -40267,7 +40267,7 @@
       <c r="L41" s="27"/>
       <c r="Q41" s="27"/>
     </row>
-    <row r="42" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>520</v>
       </c>
@@ -40301,7 +40301,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
         <v>390</v>
       </c>
@@ -40336,7 +40336,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>27</v>
       </c>
@@ -40372,7 +40372,7 @@
       <c r="L44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>508</v>
       </c>
@@ -40407,7 +40407,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>37</v>
       </c>
@@ -40440,7 +40440,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -40451,7 +40451,7 @@
       <c r="L47" s="8"/>
       <c r="Q47" s="8"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>1</v>
       </c>
@@ -40466,7 +40466,7 @@
       <c r="L48" s="6"/>
       <c r="Q48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>6</v>
       </c>
@@ -40481,7 +40481,7 @@
       <c r="L49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>3</v>
       </c>
@@ -40496,7 +40496,7 @@
       <c r="L50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>5</v>
       </c>
@@ -40511,7 +40511,7 @@
       <c r="L51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>7</v>
       </c>
@@ -40526,7 +40526,7 @@
       <c r="L52" s="6"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>2</v>
       </c>
@@ -40541,7 +40541,7 @@
       <c r="L53" s="6"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>9</v>
       </c>
@@ -40554,7 +40554,7 @@
       <c r="L54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>10</v>
       </c>
@@ -40590,7 +40590,7 @@
       </c>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>520</v>
       </c>
@@ -40620,7 +40620,7 @@
       <c r="L56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="27" t="s">
         <v>511</v>
       </c>
@@ -40657,7 +40657,7 @@
       <c r="L57" s="27"/>
       <c r="Q57" s="27"/>
     </row>
-    <row r="58" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="27" t="s">
         <v>491</v>
       </c>
@@ -40691,7 +40691,7 @@
       <c r="L58" s="27"/>
       <c r="Q58" s="27"/>
     </row>
-    <row r="59" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="27" t="s">
         <v>27</v>
       </c>
@@ -40727,7 +40727,7 @@
       <c r="L59" s="27"/>
       <c r="Q59" s="27"/>
     </row>
-    <row r="60" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="27" t="s">
         <v>76</v>
       </c>
@@ -40760,7 +40760,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="27" t="s">
         <v>77</v>
       </c>
@@ -40793,7 +40793,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="27" t="s">
         <v>74</v>
       </c>
@@ -40826,7 +40826,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -40837,7 +40837,7 @@
       <c r="L63" s="8"/>
       <c r="Q63" s="8"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>1</v>
       </c>
@@ -40852,7 +40852,7 @@
       <c r="L64" s="6"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>6</v>
       </c>
@@ -40867,7 +40867,7 @@
       <c r="L65" s="6"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>3</v>
       </c>
@@ -40882,7 +40882,7 @@
       <c r="L66" s="6"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>5</v>
       </c>
@@ -40897,7 +40897,7 @@
       <c r="L67" s="6"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>7</v>
       </c>
@@ -40912,7 +40912,7 @@
       <c r="L68" s="6"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>2</v>
       </c>
@@ -40927,7 +40927,7 @@
       <c r="L69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>9</v>
       </c>
@@ -40940,7 +40940,7 @@
       <c r="L70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>10</v>
       </c>
@@ -40976,7 +40976,7 @@
       </c>
       <c r="L71" s="5"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>483</v>
       </c>
@@ -41006,7 +41006,7 @@
       <c r="L72" s="6"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>511</v>
       </c>
@@ -41043,7 +41043,7 @@
       <c r="L73" s="27"/>
       <c r="Q73" s="27"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>27</v>
       </c>
@@ -41080,7 +41080,7 @@
       <c r="L74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>79</v>
       </c>
@@ -41119,7 +41119,7 @@
       <c r="N75" s="6"/>
       <c r="O75" s="6"/>
     </row>
-    <row r="76" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -41130,7 +41130,7 @@
       <c r="L76" s="8"/>
       <c r="Q76" s="8"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>1</v>
       </c>
@@ -41145,7 +41145,7 @@
       <c r="L77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>6</v>
       </c>
@@ -41160,7 +41160,7 @@
       <c r="L78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>3</v>
       </c>
@@ -41175,7 +41175,7 @@
       <c r="L79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>5</v>
       </c>
@@ -41190,7 +41190,7 @@
       <c r="L80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>7</v>
       </c>
@@ -41205,7 +41205,7 @@
       <c r="L81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>2</v>
       </c>
@@ -41220,7 +41220,7 @@
       <c r="L82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>9</v>
       </c>
@@ -41233,7 +41233,7 @@
       <c r="L83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>10</v>
       </c>
@@ -41269,7 +41269,7 @@
       </c>
       <c r="L84" s="5"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>511</v>
       </c>
@@ -41299,7 +41299,7 @@
       <c r="L85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="27" t="s">
         <v>465</v>
       </c>
@@ -41336,7 +41336,7 @@
       <c r="L86" s="27"/>
       <c r="Q86" s="27"/>
     </row>
-    <row r="87" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="27" t="s">
         <v>273</v>
       </c>
@@ -41373,7 +41373,7 @@
       <c r="L87" s="27"/>
       <c r="Q87" s="27"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -41408,7 +41408,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>306</v>
       </c>
@@ -41443,7 +41443,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>49</v>
       </c>
@@ -41478,7 +41478,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>37</v>
       </c>
@@ -41511,7 +41511,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>128</v>
       </c>
@@ -41544,7 +41544,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>175</v>
       </c>
@@ -41575,7 +41575,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D97" s="38"/>
     </row>
   </sheetData>
@@ -41587,17 +41587,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B0F318-8C53-4B11-8704-083389C4343A}">
   <dimension ref="A1:O97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="72.33203125" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="72.36328125" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -41612,7 +41612,7 @@
       <c r="J1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -41627,7 +41627,7 @@
       <c r="J2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -41642,7 +41642,7 @@
       <c r="J3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -41657,7 +41657,7 @@
       <c r="J4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -41672,7 +41672,7 @@
       <c r="J5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -41687,7 +41687,7 @@
       <c r="J6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -41700,7 +41700,7 @@
       <c r="J7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -41730,7 +41730,7 @@
       </c>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>456</v>
       </c>
@@ -41758,7 +41758,7 @@
       <c r="J9" s="6"/>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>64</v>
       </c>
@@ -41786,7 +41786,7 @@
       <c r="J10" s="6"/>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -41796,7 +41796,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>1</v>
       </c>
@@ -41811,7 +41811,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -41825,7 +41825,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>3</v>
       </c>
@@ -41839,7 +41839,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -41853,7 +41853,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
@@ -41867,7 +41867,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>2</v>
       </c>
@@ -41881,7 +41881,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>9</v>
       </c>
@@ -41893,7 +41893,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>10</v>
       </c>
@@ -41922,7 +41922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>256</v>
       </c>
@@ -41947,7 +41947,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
@@ -41972,7 +41972,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>79</v>
       </c>
@@ -42002,7 +42002,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>167</v>
       </c>
@@ -42027,7 +42027,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -42037,7 +42037,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>1</v>
       </c>
@@ -42052,7 +42052,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>6</v>
       </c>
@@ -42066,7 +42066,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>3</v>
       </c>
@@ -42080,7 +42080,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>11</v>
       </c>
@@ -42094,7 +42094,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>7</v>
       </c>
@@ -42108,7 +42108,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>2</v>
       </c>
@@ -42122,7 +42122,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>9</v>
       </c>
@@ -42134,7 +42134,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
@@ -42163,7 +42163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>787</v>
       </c>
@@ -42188,7 +42188,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>778</v>
       </c>
@@ -42214,7 +42214,7 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>788</v>
       </c>
@@ -42242,7 +42242,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -42252,7 +42252,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>1</v>
       </c>
@@ -42267,7 +42267,7 @@
       <c r="H37" s="5"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>6</v>
       </c>
@@ -42281,7 +42281,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>3</v>
       </c>
@@ -42295,7 +42295,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>11</v>
       </c>
@@ -42309,7 +42309,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>7</v>
       </c>
@@ -42323,7 +42323,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>2</v>
       </c>
@@ -42338,7 +42338,7 @@
       <c r="H42" s="6"/>
       <c r="L42" s="78"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>9</v>
       </c>
@@ -42350,7 +42350,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="1:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>10</v>
       </c>
@@ -42380,7 +42380,7 @@
       </c>
       <c r="L44" s="78"/>
     </row>
-    <row r="45" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A45" s="6" t="s">
         <v>788</v>
       </c>
@@ -42406,7 +42406,7 @@
       </c>
       <c r="L45" s="79"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>778</v>
       </c>
@@ -42435,7 +42435,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>780</v>
       </c>
@@ -42461,7 +42461,7 @@
       </c>
       <c r="L47" s="79"/>
     </row>
-    <row r="48" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48" s="6" t="s">
         <v>791</v>
       </c>
@@ -42487,7 +42487,7 @@
       </c>
       <c r="L48" s="79"/>
     </row>
-    <row r="49" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>794</v>
       </c>
@@ -42513,7 +42513,7 @@
       </c>
       <c r="L49" s="79"/>
     </row>
-    <row r="50" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>795</v>
       </c>
@@ -42539,7 +42539,7 @@
       </c>
       <c r="L50" s="79"/>
     </row>
-    <row r="51" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>797</v>
       </c>
@@ -42565,7 +42565,7 @@
       </c>
       <c r="L51" s="79"/>
     </row>
-    <row r="52" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>799</v>
       </c>
@@ -42591,7 +42591,7 @@
       </c>
       <c r="L52" s="79"/>
     </row>
-    <row r="53" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>142</v>
       </c>
@@ -42617,7 +42617,7 @@
       </c>
       <c r="L53" s="79"/>
     </row>
-    <row r="54" spans="1:12" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -42643,7 +42643,7 @@
       </c>
       <c r="L54" s="79"/>
     </row>
-    <row r="55" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -42653,7 +42653,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>1</v>
       </c>
@@ -42668,7 +42668,7 @@
       <c r="H56" s="5"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>6</v>
       </c>
@@ -42682,7 +42682,7 @@
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>3</v>
       </c>
@@ -42696,7 +42696,7 @@
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>11</v>
       </c>
@@ -42710,7 +42710,7 @@
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>7</v>
       </c>
@@ -42724,7 +42724,7 @@
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>2</v>
       </c>
@@ -42738,7 +42738,7 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>9</v>
       </c>
@@ -42750,7 +42750,7 @@
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>10</v>
       </c>
@@ -42779,7 +42779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>475</v>
       </c>
@@ -42804,7 +42804,7 @@
         <v>LIB raw materials</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>27</v>
       </c>
@@ -42830,34 +42830,34 @@
         <v>ecoinvent-3.10-cutoff</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C70" s="59"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C71" s="59"/>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C83" s="37"/>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C87" s="59"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C89" s="82"/>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
       <c r="E93" s="81"/>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C97" s="80"/>
     </row>
   </sheetData>
@@ -42872,31 +42872,31 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.6328125" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.6328125" customWidth="1"/>
+    <col min="5" max="5" width="35.08984375" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" customWidth="1"/>
-    <col min="8" max="8" width="30.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.36328125" customWidth="1"/>
+    <col min="8" max="8" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="61" t="s">
         <v>713</v>
       </c>
       <c r="B3" s="61"/>
       <c r="C3" s="61"/>
     </row>
-    <row r="5" spans="1:11" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="63" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="64" t="s">
         <v>650</v>
       </c>
@@ -42923,11 +42923,11 @@
       <c r="J5" s="62"/>
       <c r="K5" s="62"/>
     </row>
-    <row r="6" spans="1:11" s="63" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="95" t="s">
+    <row r="6" spans="1:11" s="63" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="86" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="88" t="s">
         <v>695</v>
       </c>
       <c r="C6" s="70" t="s">
@@ -42952,9 +42952,9 @@
       <c r="J6" s="62"/>
       <c r="K6" s="62"/>
     </row>
-    <row r="7" spans="1:11" s="63" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="96"/>
-      <c r="B7" s="86"/>
+    <row r="7" spans="1:11" s="63" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="87"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="66" t="s">
         <v>701</v>
       </c>
@@ -42977,11 +42977,11 @@
       <c r="J7" s="62"/>
       <c r="K7" s="62"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="92" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="88" t="s">
         <v>695</v>
       </c>
       <c r="C8" s="70" t="s">
@@ -43003,9 +43003,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
-      <c r="B9" s="86"/>
+    <row r="9" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="92"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="66" t="s">
         <v>701</v>
       </c>
@@ -43025,9 +43025,9 @@
         <v>696</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="93"/>
-      <c r="B10" s="86" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="92"/>
+      <c r="B10" s="88" t="s">
         <v>698</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -43049,9 +43049,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="93"/>
-      <c r="B11" s="86"/>
+    <row r="11" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="92"/>
+      <c r="B11" s="88"/>
       <c r="C11" s="66" t="s">
         <v>701</v>
       </c>
@@ -43071,9 +43071,9 @@
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
-      <c r="B12" s="86" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="92"/>
+      <c r="B12" s="88" t="s">
         <v>191</v>
       </c>
       <c r="C12" s="70" t="s">
@@ -43095,9 +43095,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="86"/>
+    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="93"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="66" t="s">
         <v>701</v>
       </c>
@@ -43117,11 +43117,11 @@
         <v>700</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="92" t="s">
+    <row r="14" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="89" t="s">
         <v>469</v>
       </c>
       <c r="C14" s="70" t="s">
@@ -43143,9 +43143,9 @@
         <v>759</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
-      <c r="B15" s="89"/>
+    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="92"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="66" t="s">
         <v>701</v>
       </c>
@@ -43165,9 +43165,9 @@
         <v>752</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
-      <c r="B16" s="90" t="s">
+    <row r="16" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="92"/>
+      <c r="B16" s="95" t="s">
         <v>471</v>
       </c>
       <c r="C16" s="70" t="s">
@@ -43189,9 +43189,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-      <c r="B17" s="91"/>
+    <row r="17" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A17" s="92"/>
+      <c r="B17" s="96"/>
       <c r="C17" s="66" t="s">
         <v>701</v>
       </c>
@@ -43211,9 +43211,9 @@
         <v>763</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-      <c r="B18" s="90" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="92"/>
+      <c r="B18" s="95" t="s">
         <v>472</v>
       </c>
       <c r="C18" s="70" t="s">
@@ -43235,9 +43235,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="94"/>
-      <c r="B19" s="91"/>
+    <row r="19" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="93"/>
+      <c r="B19" s="96"/>
       <c r="C19" s="66" t="s">
         <v>701</v>
       </c>
@@ -43258,11 +43258,11 @@
       </c>
       <c r="K19" s="77"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="92" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="95" t="s">
         <v>722</v>
       </c>
       <c r="C20" s="70" t="s">
@@ -43285,9 +43285,9 @@
       </c>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="94"/>
-      <c r="B21" s="91"/>
+    <row r="21" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A21" s="93"/>
+      <c r="B21" s="96"/>
       <c r="C21" s="66" t="s">
         <v>701</v>
       </c>
@@ -43308,11 +43308,11 @@
       </c>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="87" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="94" t="s">
         <v>721</v>
       </c>
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="89" t="s">
         <v>511</v>
       </c>
       <c r="C22" s="70" t="s">
@@ -43334,9 +43334,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="89"/>
+    <row r="23" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="94"/>
+      <c r="B23" s="90"/>
       <c r="C23" s="66" t="s">
         <v>701</v>
       </c>
@@ -43357,9 +43357,9 @@
       </c>
       <c r="K23" s="74"/>
     </row>
-    <row r="24" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="88" t="s">
+    <row r="24" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="94"/>
+      <c r="B24" s="89" t="s">
         <v>483</v>
       </c>
       <c r="C24" s="70" t="s">
@@ -43381,9 +43381,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="89"/>
+    <row r="25" spans="1:11" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="94"/>
+      <c r="B25" s="90"/>
       <c r="C25" s="66" t="s">
         <v>701</v>
       </c>
@@ -43403,9 +43403,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="86" t="s">
+    <row r="26" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="94"/>
+      <c r="B26" s="88" t="s">
         <v>520</v>
       </c>
       <c r="C26" s="70" t="s">
@@ -43427,9 +43427,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="86"/>
+    <row r="27" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A27" s="94"/>
+      <c r="B27" s="88"/>
       <c r="C27" s="66" t="s">
         <v>701</v>
       </c>
@@ -43449,9 +43449,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
-      <c r="B28" s="86" t="s">
+    <row r="28" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="94"/>
+      <c r="B28" s="88" t="s">
         <v>486</v>
       </c>
       <c r="C28" s="70" t="s">
@@ -43473,9 +43473,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
-      <c r="B29" s="86"/>
+    <row r="29" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="94"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="66" t="s">
         <v>701</v>
       </c>
@@ -43495,9 +43495,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="87"/>
-      <c r="B30" s="86" t="s">
+    <row r="30" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="94"/>
+      <c r="B30" s="88" t="s">
         <v>487</v>
       </c>
       <c r="C30" s="70" t="s">
@@ -43519,9 +43519,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="87"/>
-      <c r="B31" s="86"/>
+    <row r="31" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A31" s="94"/>
+      <c r="B31" s="88"/>
       <c r="C31" s="66" t="s">
         <v>701</v>
       </c>
@@ -43541,9 +43541,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="86" t="s">
+    <row r="32" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
+      <c r="B32" s="88" t="s">
         <v>490</v>
       </c>
       <c r="C32" s="70" t="s">
@@ -43565,9 +43565,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="86"/>
+    <row r="33" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="88"/>
       <c r="C33" s="66" t="s">
         <v>701</v>
       </c>
@@ -43589,14 +43589,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A8:A13"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="A22:A33"/>
     <mergeCell ref="B14:B15"/>
@@ -43608,6 +43600,14 @@
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A8:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
